--- a/InputData/elec/BDSBaPCF/Boolean Do Suppliers Bid at Peak Capacity Factors.xlsx
+++ b/InputData/elec/BDSBaPCF/Boolean Do Suppliers Bid at Peak Capacity Factors.xlsx
@@ -1,37 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-us\InputData\elec\BDSBaPCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BDSBaPCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8784E3-51DD-421C-A50A-EB476C2E8047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="45" windowWidth="23955" windowHeight="11580"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="12645" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BDSBaPCF" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>BDSBaPCF Boolean Do Suppliers Bid at Peak Capacity Factors</t>
   </si>
   <si>
+    <t>Iowa</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>None needed.  See notes below.</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>natural gas nonpeaker</t>
+    <t>Certain plant types, such as coal and natural gas, are capable of running for most</t>
+  </si>
+  <si>
+    <t>of the year (at their Peak Time capacity factors), if there were demand for their</t>
+  </si>
+  <si>
+    <t>services.  Other plant types, such as solar, wind, and hydro, are limited to a</t>
+  </si>
+  <si>
+    <t>much smaller fraction of the year by physical constraints (such as lack of sunlight</t>
+  </si>
+  <si>
+    <t>during some hours).</t>
+  </si>
+  <si>
+    <t>When bidding for how much power they are willing to supply, plant operators</t>
+  </si>
+  <si>
+    <t>that can supply more power are likely to bid it, since they will make more money</t>
+  </si>
+  <si>
+    <t>if they are able to run their coal or even a relatively inefficient peaker plant</t>
+  </si>
+  <si>
+    <t>more often.  (As long as the plant is built, they want to get use out of it.)</t>
+  </si>
+  <si>
+    <t>This variable helps the model decide which capacity factors best represent</t>
+  </si>
+  <si>
+    <t>the ones a plant owner would bid (offer to sell), which guides the dispatch</t>
+  </si>
+  <si>
+    <t>mechanism.  Plants that could conceivably be run full-out all year (minus</t>
+  </si>
+  <si>
+    <t>required maintenance, etc.) bid at their Peak Capacity Factors;</t>
+  </si>
+  <si>
+    <t>other plants bid at their Expected Capacity Factors, which account for all</t>
+  </si>
+  <si>
+    <t>of the things that prevent a plant from running at its peak all the time.</t>
+  </si>
+  <si>
+    <t>For the United States, we have set coal to 0 as of version 3.4. This reflects</t>
+  </si>
+  <si>
+    <t>the fact that certain air quality / environmental restrictions, as well as current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supply chain logistics, limit the amount the coal dispatches annually. </t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (Boolean)</t>
+  </si>
+  <si>
+    <t>Do Suppliers Bid at Peak Capacity Factors</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
   </si>
   <si>
     <t>nuclear</t>
@@ -40,6 +126,9 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
     <t>solar PV</t>
   </si>
   <si>
@@ -58,63 +147,9 @@
     <t>natural gas peaker</t>
   </si>
   <si>
-    <t>Certain plant types, such as coal and natural gas, are capable of running for most</t>
-  </si>
-  <si>
-    <t>of the year (at their Peak Time capacity factors), if there were demand for their</t>
-  </si>
-  <si>
-    <t>services.  Other plant types, such as solar, wind, and hydro, are limited to a</t>
-  </si>
-  <si>
-    <t>much smaller fraction of the year by physical constraints (such as lack of sunlight</t>
-  </si>
-  <si>
-    <t>during some hours).</t>
-  </si>
-  <si>
-    <t>When bidding for how much power they are willing to supply, plant operators</t>
-  </si>
-  <si>
-    <t>that can supply more power are likely to bid it, since they will make more money</t>
-  </si>
-  <si>
-    <t>if they are able to run their coal or even a relatively inefficient peaker plant</t>
-  </si>
-  <si>
-    <t>more often.  (As long as the plant is built, they want to get use out of it.)</t>
-  </si>
-  <si>
-    <t>This variable helps the model decide which capacity factors best represent</t>
-  </si>
-  <si>
-    <t>the ones a plant owner would bid (offer to sell), which guides the dispatch</t>
-  </si>
-  <si>
-    <t>mechanism.  Plants that could conceivably be run full-out all year (minus</t>
-  </si>
-  <si>
-    <t>required maintenance, etc.) bid at their Peak Capacity Factors;</t>
-  </si>
-  <si>
-    <t>other plants bid at their Expected Capacity Factors, which account for all</t>
-  </si>
-  <si>
-    <t>of the things that prevent a plant from running at its peak all the time.</t>
-  </si>
-  <si>
-    <t>None needed.  See notes below.</t>
-  </si>
-  <si>
     <t>lignite</t>
   </si>
   <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
     <t>offshore wind</t>
   </si>
   <si>
@@ -127,14 +162,32 @@
     <t>municipal solid waste</t>
   </si>
   <si>
-    <t>Do Suppliers Bid at Peak Capacity Factors (Boolean)</t>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,13 +203,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -171,11 +245,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -195,9 +274,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -235,9 +314,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -272,7 +351,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -307,7 +386,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,101 +559,119 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -583,33 +680,36 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
     <col min="2" max="2" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -617,15 +717,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -633,7 +733,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -641,7 +741,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -649,7 +749,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -657,23 +757,23 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -681,7 +781,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -689,50 +789,115 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B13">
-        <f>B2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <f>B6</f>
+        <f>B2</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B15">
-        <f>B11</f>
+        <f>B7</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B16">
-        <f>B11</f>
+        <f>B12</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B17">
-        <f>B9</f>
+        <f>B12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18">
+        <f>B10</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>